--- a/docs/Login-Instruktur-UNTAR.xlsx
+++ b/docs/Login-Instruktur-UNTAR.xlsx
@@ -519,7 +519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -551,7 +551,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
@@ -600,7 +599,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>fendy</t>
+          <t>fendyher</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -630,7 +629,7 @@
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>indahUNTAR</t>
+          <t>indahper</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
@@ -660,7 +659,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>linaMKUNTAR</t>
+          <t>linalind</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -690,7 +689,7 @@
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>listyUNTAR</t>
+          <t>listya</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
@@ -720,7 +719,7 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>naokkiUNTAR</t>
+          <t>naokki</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -750,7 +749,7 @@
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>vaniaUNTAR</t>
+          <t>vaniah</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
@@ -780,7 +779,7 @@
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>vinnyUNTAR</t>
+          <t>vinnyy</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
@@ -789,6 +788,36 @@
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>SUKSES</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Kezia</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>UNTAR</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>keziaa</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>12345678</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
         <is>
           <t>SUKSES</t>
         </is>
